--- a/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
+++ b/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
@@ -8,11 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海天径1号 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="舂磡角道44号 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="舂磡角道46号 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="舂磡角道48号 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="舂磡角道50号 销控表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -908,12 +904,16 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>海天径 1号, 舂磡角道 44, 46, 48, 50号 - 海天径1号 销控网格图</t>
+          <t>海天径 1号, 舂磡角道 44, 46, 48, 50号 - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -977,520 +977,97 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>5 套</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>楼层\房号</t>
+          <t>类型/位置</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
+          <t>海天径1号</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>舂磡角道44号</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>舂磡角道46号</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>舂磡角道48号</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>舂磡角道50号</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>/F</t>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>- | 4238呎 (4+房)
+          <t>海天径1号
+4238呎 (4+房)
+(待售)
 暂无价格
-暂无呎价
-(待售)</t>
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>舂磡角道44号
+4215呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>舂磡角道46号
+4254呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>舂磡角道48号
+6350呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>舂磡角道50号
+6364呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海天径 1号, 舂磡角道 44, 46, 48, 50号 - 舂磡角道44号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>- | 4215呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海天径 1号, 舂磡角道 44, 46, 48, 50号 - 舂磡角道46号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>- | 4254呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海天径 1号, 舂磡角道 44, 46, 48, 50号 - 舂磡角道48号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>- | 6350呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海天径 1号, 舂磡角道 44, 46, 48, 50号 - 舂磡角道50号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>- | 6364呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
+++ b/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +96,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -212,7 +217,7 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -660,7 +665,7 @@
           <t>海天径1号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -706,7 +711,7 @@
           <t>舂磡角道44号</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -752,7 +757,7 @@
           <t>舂磡角道46号</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -798,7 +803,7 @@
           <t>舂磡角道48号</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -844,7 +849,7 @@
           <t>舂磡角道50号</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>-</t>

--- a/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
+++ b/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
@@ -665,7 +665,7 @@
           <t>海天径1号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -711,7 +711,7 @@
           <t>舂磡角道44号</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -757,7 +757,7 @@
           <t>舂磡角道46号</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -803,7 +803,7 @@
           <t>舂磡角道48号</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>-</t>
@@ -849,7 +849,7 @@
           <t>舂磡角道50号</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>-</t>

--- a/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
+++ b/files/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -598,6 +598,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -655,6 +659,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -701,6 +725,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -747,6 +791,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -793,6 +857,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -839,6 +923,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -885,13 +989,33 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
